--- a/data/Individuals - frequency of internet use_transformed.xlsx
+++ b/data/Individuals - frequency of internet use_transformed.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 42 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 42 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 42 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 42 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 42 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 42 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 41 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 41 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 41 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 41 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 41 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 41 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 41 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 40 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 40 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 40 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 40 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 40 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 40 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 39 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 39 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 39 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 39 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 39 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 39 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 38 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 38 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 38 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 38 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 38 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 38 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 37 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 37 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 37 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 37 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 37 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 37 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 36 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 36 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 36 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 36 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 36 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 36 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 35 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 35 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 35 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 35 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 35 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 35 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 34 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 34 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 34 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 34 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 34 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 34 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 33 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 33 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 33 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 33 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 33 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 33 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 32 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 32 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 32 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 32 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 32 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 32 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 31 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 31 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 31 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 31 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 31 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 31 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 31 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 30 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 30 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 30 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 30 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 30 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 30 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 29 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 29 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 29 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 29 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 29 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 29 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 28 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 28 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 28 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 28 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 28 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 28 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 27 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 27 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 27 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 27 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 27 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 27 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 26 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 26 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 26 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 26 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 26 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 26 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 25 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 25 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 25 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 25 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 25 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 25 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 25 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 24 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 24 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 24 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 24 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 24 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 24 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 23 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 23 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 23 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 23 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 23 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 23 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 22 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 22 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 22 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 22 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 22 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 22 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 21 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 21 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 21 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 21 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 21 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 21 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 20 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 20 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 20 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 20 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 20 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 20 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 19 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 19 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 19 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 19 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 19 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 19 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 18 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 18 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 18 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 18 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 18 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 18 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 17 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 17 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 17 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 17 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 17 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 17 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 16 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 16 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 16 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 16 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 16 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 16 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 16 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 15 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 15 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 15 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 15 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 15 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 15 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 14 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 14 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 14 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 14 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 14 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 14 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 13 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 13 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 13 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 13 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 13 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 13 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 12 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 12 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 12 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 12 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 12 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 12 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 11 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 11 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 11 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 11 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 11 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 11 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 10 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 10 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 10 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 10 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 10 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 10 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 09 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 09 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 09 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 09 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 09 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 09 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 03 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 03 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 03 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 03 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 03 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 03 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 02 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 02 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 02 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 02 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 02 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 02 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 01 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 01 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 01 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 01 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 01 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 01 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 00 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 00 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 00 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 00 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 00 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 27 MINUTES 00 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 59 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 59 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 59 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 59 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 59 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 59 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 58 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 58 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 58 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 58 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 58 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 58 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 58 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 57 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 57 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 57 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 57 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 57 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 57 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 56 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 56 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 56 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 56 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 56 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 56 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 55 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 55 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 55 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 55 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 55 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 55 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 54 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 54 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 54 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 54 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 54 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 54 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 53 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 53 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 53 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 53 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 53 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 53 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 52 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 52 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 52 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 52 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 52 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 52 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 51 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 51 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 51 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 51 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 51 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 51 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 50 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 50 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 50 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 50 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 50 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 50 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 50 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -8026,7 +8026,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 42 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 42 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 42 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 42 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 42 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 42 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 41 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 41 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 41 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 41 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 41 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 41 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 41 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 40 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 40 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 40 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -9162,7 +9162,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 40 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 40 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 40 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 39 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 39 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 39 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 39 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 39 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 39 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 38 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 38 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 38 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 38 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 38 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 38 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 37 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 37 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 37 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 37 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 37 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 37 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 36 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 36 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 36 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 36 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 36 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 36 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 35 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 35 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 35 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 35 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 35 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 35 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 34 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 34 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 34 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 34 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 34 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 34 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 33 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 33 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 33 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 33 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 33 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 33 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 32 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 32 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 32 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 32 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 32 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 32 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 31 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 31 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 31 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 31 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 31 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 31 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 30 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 30 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 30 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 30 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 30 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 30 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 29 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -10442,7 +10442,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 29 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 29 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 29 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 29 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 29 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 28 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 28 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 28 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 28 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 28 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 28 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 27 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 27 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 27 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 27 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 27 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 27 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 26 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 26 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 26 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 26 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 26 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 26 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 25 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 25 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 25 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -10954,7 +10954,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 25 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 25 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 25 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 24 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 24 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 24 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 24 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 24 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 24 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 23 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 23 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 23 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -11186,7 +11186,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 23 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 23 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 23 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 22 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 22 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 22 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 22 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 22 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 22 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 21 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 21 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 21 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 21 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 21 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 21 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 20 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 20 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 20 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 20 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 20 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 20 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 19 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 19 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 19 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 19 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 19 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 19 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 18 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 18 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 18 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 18 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 18 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 18 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 17 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -11866,7 +11866,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 17 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 17 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 17 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 17 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -11946,7 +11946,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 17 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 16 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 16 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 16 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 16 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -12046,7 +12046,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 16 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -12066,7 +12066,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 16 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 15 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 15 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 15 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 15 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 15 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -12186,7 +12186,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 15 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 14 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -12226,7 +12226,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 14 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 14 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 14 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 14 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -12306,7 +12306,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 14 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 13 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 13 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 13 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 13 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 13 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 13 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 12 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 12 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 12 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 12 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 12 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 12 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 11 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 11 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 11 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 11 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 11 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 11 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 10 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 10 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 10 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 10 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 10 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 10 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 09 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 09 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 09 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 09 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 09 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 09 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -13006,7 +13006,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 08 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -13126,7 +13126,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 07 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -13206,7 +13206,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 06 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -13306,7 +13306,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -13346,7 +13346,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -13366,7 +13366,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 05 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 04 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 03 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 03 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 03 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -13606,7 +13606,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 03 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 03 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 03 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 02 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 02 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 02 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 02 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -13746,7 +13746,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 02 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 02 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 01 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 01 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 01 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 01 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 01 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 01 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 00 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 00 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 00 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 00 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 00 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 26 MINUTES 00 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 59 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 59 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 59 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 59 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 59 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -14126,7 +14126,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 59 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 58 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 58 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 58 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -14206,7 +14206,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 58 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 58 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -14246,7 +14246,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 58 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 57 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -14286,7 +14286,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 57 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 57 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 57 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 57 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 57 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -14386,7 +14386,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 56 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 56 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -14426,7 +14426,7 @@
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 56 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 56 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
@@ -14466,7 +14466,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 56 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 56 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
@@ -14506,7 +14506,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 55 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 55 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 55 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
@@ -14566,7 +14566,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 55 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 55 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 55 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -14626,7 +14626,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 54 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 54 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 54 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -14686,7 +14686,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 54 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 54 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 54 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -14746,7 +14746,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 53 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 53 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -14786,7 +14786,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 53 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -14806,7 +14806,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 53 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 53 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 53 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 52 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 52 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 52 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 52 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 52 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -14958,7 +14958,7 @@
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 52 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 51 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 51 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 51 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 51 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 51 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 51 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 50 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -15112,7 +15112,7 @@
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 50 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 50 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 50 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -15170,7 +15170,7 @@
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 50 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -15190,7 +15190,7 @@
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 50 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -15230,7 +15230,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 49 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -15330,7 +15330,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -15370,7 +15370,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -15430,7 +15430,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 48 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 47 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -15606,7 +15606,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: legalább hetente egyszer (de nem minden nap)</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 46 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: naponta</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -15776,7 +15776,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 45 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -15832,7 +15832,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente kevesebb mint egyszer</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 44 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -15926,7 +15926,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>MYMEMORY WARNING: YOU USED ALL AVAILABLE FREE TRANSLATIONS FOR TODAY. NEXT AVAILABLE IN  22 HOURS 25 MINUTES 43 SECONDS VISIT HTTPS://MYMEMORY.TRANSLATED.NET/DOC/USAGELIMITS.PHP TO TRANSLATE MORE</t>
+          <t>Az internet-hozzáférés gyakorisága: hetente egyszer (minden napot beleértve)</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
